--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B178"/>
+  <dimension ref="A1:B181"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1825,9 +1825,33 @@
         <v>Ogiltig ICC-profil (header-signatur saknas).</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>Standard datasets</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Standarddatauppsättningar</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>Loading…</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Läser in…</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>Failed to load list</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Det gick inte att läsa in listan</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B178"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -585,12 +585,12 @@
     </row>
     <row r="24" xml:space="preserve">
       <c r="A24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Select files:
-characterization data or ICC profiles</v>
+        <v xml:space="preserve">characterization data
+or ICC profiles</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Välj filer:
-karakteriseringsdata eller ICC-profiler</v>
+        <v xml:space="preserve">karakteriseringsdata
+eller ICC-profiler</v>
       </c>
     </row>
     <row r="25">

--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B185"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1849,9 +1849,41 @@
         <v>Det gick inte att läsa in listan</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>Thickness:</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Tjocklek:</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>Fall-off:</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Övergång:</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>Hard</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Hård</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>Soft</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Mjuk</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B185"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B189"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1881,9 +1881,41 @@
         <v>Mjuk</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>G7 validation is not available for ICC profiles.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>G7-validering är inte tillgänglig för ICC-profiler.</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>ICC vs ICC comparison requires CMYK profiles.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>ICC-mot-ICC-jämförelse kräver CMYK-profiler.</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>Dataset B does not contain colorants matching ICC profile A.</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Datamängd B innehåller inga färgmedel som matchar ICC-profil A.</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>Dataset A does not contain colorants matching ICC profile B.</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Datamängd A innehåller inga färgmedel som matchar ICC-profil B.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B185"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B192"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1913,9 +1913,33 @@
         <v>Datamängd A innehåller inga färgmedel som matchar ICC-profil B.</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Header</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Header</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Tags</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Taggar</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Loading ICC viewer…</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Läser in ICC-visare…</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B192"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B192"/>
+  <dimension ref="A1:B193"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1937,9 +1937,17 @@
         <v>Läser in ICC-visare…</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Launch editor</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Öppna redigerare</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B192"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B193"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1945,9 +1945,25 @@
         <v>Öppna redigerare</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>All data stays local to browser</v>
+      </c>
+      <c r="B194" t="str">
+        <v>All data stannar lokalt i webbläsaren</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Free browser-resident online tool</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Gratis onlineverktyg som körs i webbläsaren</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B195"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -1561,12 +1561,14 @@
         <v>Inga spektraldata — växla till färgtonvärde (CTV)</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>No primary tone steps found.\nNeeds rows with a single non-zero colorant.</v>
-      </c>
-      <c r="B146" t="str">
-        <v>Inga primära tonsteg hittades.\nKräver rader med ett enda nollskilt färgämne.</v>
+    <row r="146" xml:space="preserve">
+      <c r="A146" t="str" xml:space="preserve">
+        <v xml:space="preserve">No primary tone steps found.
+Needs rows with a single non-zero colorant.</v>
+      </c>
+      <c r="B146" t="str" xml:space="preserve">
+        <v xml:space="preserve">Inga primära tonsteg hittades.
+Kräver rader med ett enda nollskilt färgämne.</v>
       </c>
     </row>
     <row r="147">
@@ -1609,20 +1611,24 @@
         <v>↻ Återskapa</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>Input\ncolorant</v>
-      </c>
-      <c r="B152" t="str">
-        <v>Ingångs-\nfärgämne</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>Nearest\nin dataset</v>
-      </c>
-      <c r="B153" t="str">
-        <v>Närmaste\ni datamängd</v>
+    <row r="152" xml:space="preserve">
+      <c r="A152" t="str" xml:space="preserve">
+        <v xml:space="preserve">Input
+colorant</v>
+      </c>
+      <c r="B152" t="str" xml:space="preserve">
+        <v xml:space="preserve">Ingångs-
+färgämne</v>
+      </c>
+    </row>
+    <row r="153" xml:space="preserve">
+      <c r="A153" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nearest
+in dataset</v>
+      </c>
+      <c r="B153" t="str" xml:space="preserve">
+        <v xml:space="preserve">Närmaste
+i datamängd</v>
       </c>
     </row>
     <row r="154">

--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B195"/>
+  <dimension ref="A1:B205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1967,9 +1967,89 @@
         <v>Gratis onlineverktyg som körs i webbläsaren</v>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Image</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Bild</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Load Image</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Läs in bild</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Bind image to dataset</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Koppla bild till dataset</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Remove image</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Ta bort bild</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>Image color space: {cs} {src}</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Bildens färgrymd: {cs} {src}</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Bound to {name} — {n} points</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Kopplad till {name} — {n} punkter</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Lab image — {n} points</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Lab-bild — {n} punkter</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Cannot bind: image is {img} but Dataset {slot} is {family}.</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Kan inte koppla: bilden är {img} men dataset {slot} är {family}.</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Unsupported image format. Use PNG, JPEG, or TIFF.</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Bildformatet stöds inte. Använd PNG, JPEG eller TIFF.</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>“{name}” is too large ({mb} MB). Maximum image size is {max} MB.</v>
+      </c>
+      <c r="B205" t="str">
+        <v>”{name}” är för stor ({mb} MB). Maximal bildstorlek: {max} MB.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B205"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B205"/>
+  <dimension ref="A1:B224"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2033,10 +2033,10 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Unsupported image format. Use PNG, JPEG, or TIFF.</v>
+        <v>Unsupported image format. Use PNG, JPEG, TIFF, BMP, GIF, or PDF.</v>
       </c>
       <c r="B204" t="str">
-        <v>Bildformatet stöds inte. Använd PNG, JPEG eller TIFF.</v>
+        <v>Bildformatet stöds inte. Använd PNG, JPEG, TIFF, BMP, GIF eller PDF.</v>
       </c>
     </row>
     <row r="205">
@@ -2047,9 +2047,161 @@
         <v>”{name}” är för stor ({mb} MB). Maximal bildstorlek: {max} MB.</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Embedded: {name}</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Inbäddad: {name}</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Decoding image…</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Avkodar bild…</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Image file is too small or corrupt.</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Bildfilen är för liten eller skadad.</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>TIFF decoder library failed to load.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>TIFF-avkodningsbiblioteket kunde inte läsas in.</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Selected dataset model is still loading — try again in a moment.</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Det valda dataset-modellen läses fortfarande in — försök igen om en stund.</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Image decode failed.</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Bildavkodningen misslyckades.</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Dataset {slot} is not loaded.</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Dataset {slot} är inte inläst.</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Embedded profile is no longer available.</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Den inbäddade profilen är inte längre tillgänglig.</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>(from embedded ICC)</v>
+      </c>
+      <c r="B214" t="str">
+        <v>(från inbäddad ICC)</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>(TIFF Lab)</v>
+      </c>
+      <c r="B215" t="str">
+        <v>(TIFF Lab)</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>(inferred from channels)</v>
+      </c>
+      <c r="B216" t="str">
+        <v>(härlett från kanaler)</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>{n} representative points after binning + dedupe</v>
+      </c>
+      <c r="B217" t="str">
+        <v>{n} representativa punkter efter binning + deduplicering</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>PDF support is limited to single-image Photoshop PDFs. Save as TIFF, JPEG, PNG, BMP, or GIF for other PDF content.</v>
+      </c>
+      <c r="B218" t="str">
+        <v>PDF-stöd är begränsat till Photoshop-PDF med en enda bild. Spara som TIFF, JPEG, PNG, BMP eller GIF för annat PDF-innehåll.</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Encrypted PDFs are not supported.</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Krypterade PDF:er stöds inte.</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Only single-page Photoshop PDFs are supported.</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Endast ensidiga Photoshop-PDF:er stöds.</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>PDF structure could not be parsed.</v>
+      </c>
+      <c r="B221" t="str">
+        <v>PDF-strukturen kunde inte tolkas.</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>No image found inside the PDF.</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Ingen bild hittades i PDF:en.</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>PDF colour space is not supported. Use Gray, RGB, CMYK, or an ICC-based profile.</v>
+      </c>
+      <c r="B223" t="str">
+        <v>PDF-färgrymden stöds inte. Använd Grå, RGB, CMYK eller en ICC-baserad profil.</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>PDF image filter is not supported. Re-save the PDF with JPEG or ZIP compression.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>PDF-bildfiltret stöds inte. Spara om PDF:en med JPEG- eller ZIP-komprimering.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B224"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B224"/>
+  <dimension ref="A1:B242"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2199,9 +2199,153 @@
         <v>PDF-bildfiltret stöds inte. Spara om PDF:en med JPEG- eller ZIP-komprimering.</v>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close file select</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Stäng filval</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Drag to resize</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Dra för att ändra storlek</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Contact</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Kontakt</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>Remove file</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Ta bort fil</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>Rendering intent:</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Renderingsintention:</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>Perceptual</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Perceptuell</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>Relative Colorimetric</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Relativ kolorimetrisk</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Saturation</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Mättnad</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Absolute Colorimetric</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Absolut kolorimetrisk</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>System default ({lang})</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Systemstandard ({lang})</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>ICC load error: {msg}</v>
+      </c>
+      <c r="B235" t="str">
+        <v>ICC-laddningsfel: {msg}</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>Could not parse ICC profile: {msg}</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Det gick inte att tolka ICC-profilen: {msg}</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Popup blocked — allow popups for this site to launch the editor.</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Popup blockerad — tillåt popup-fönster för den här webbplatsen för att starta redigeraren.</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Failed to load {name}: {msg}</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Det gick inte att läsa in {name}: {msg}</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Color space</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Färgrymd</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Device class</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Enhetsklass</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Colorants</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Färgmedel</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>Rendering intents</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Renderingsintentioner</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B224"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B242"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B242"/>
+  <dimension ref="A1:B244"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2343,9 +2343,25 @@
         <v>Renderingsintentioner</v>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>ICC A2B Evaluation</v>
+      </c>
+      <c r="B243" t="str">
+        <v>ICC A2B-utvärdering</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>ICC Output</v>
+      </c>
+      <c r="B244" t="str">
+        <v>ICC-utdata</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B242"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B244"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B244"/>
+  <dimension ref="A1:B248"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2359,9 +2359,41 @@
         <v>ICC-utdata</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>Image detail</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Bilddetalj</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>Coarse</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Grov</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>Standard</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>Fine</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Fin</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B244"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B248"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B248"/>
+  <dimension ref="A1:B263"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2391,9 +2391,129 @@
         <v>Fin</v>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Prenumerera</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Get notified about new chardata releases</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Få besked om nya chardata-releaser</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Få besked om nya releaser</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>We’ll email you when a new major or minor chardata release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Vi mejlar dig när en ny större eller mindre chardata-release släpps. Patch-releaser hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B254" t="str">
+        <v>E-postadress</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B255" t="str">
+        <v>du@exempel.com</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>How will you use chardata?</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Hur kommer du att använda chardata?</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B257" t="str">
+        <v>(valfritt)</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B258" t="str">
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>I agree to receive emails about chardata releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Jag godkänner att få e-post om chardata-releaser. Jag kan avsluta prenumerationen när som helst.</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Prenumerera</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Tack — vi hör av oss.</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new chardata release ships.</v>
+      </c>
+      <c r="B262" t="str">
+        <v>När du har godkänts får du ett välkomstmeddelande. Sedan hör vi av oss endast när en ny chardata-release släpps.</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B248"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B263"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B263"/>
+  <dimension ref="A1:B264"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2511,9 +2511,17 @@
         <v>Stäng</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Integritetsmeddelande</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B263"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B264"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -2097,10 +2097,10 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Dataset {slot} is not loaded.</v>
+        <v>No color dataset loaded.</v>
       </c>
       <c r="B212" t="str">
-        <v>Dataset {slot} är inte inläst.</v>
+        <v>Inget färgdataset har lästs in.</v>
       </c>
     </row>
     <row r="213">

--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -1897,10 +1897,10 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>ICC vs ICC comparison requires CMYK profiles.</v>
+        <v>ICC vs ICC comparison requires identical colorant lists. Profile A: {a}. Profile B: {b}.</v>
       </c>
       <c r="B187" t="str">
-        <v>ICC-mot-ICC-jämförelse kräver CMYK-profiler.</v>
+        <v>ICC-mot-ICC-jämförelse kräver identiska färgmedelslistor. Profil A: {a}. Profil B: {b}.</v>
       </c>
     </row>
     <row r="188">

--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B264"/>
+  <dimension ref="A1:B269"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2519,9 +2519,49 @@
         <v>Integritetsmeddelande</v>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Measurement-only data (no device colorants): 3D and 2D-slice point cloud, data table, and label-matched compare are available; gamut shell, extract, tone value, estimate, and validation are disabled.</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Endast mätdata (inga enhetsfärgämnen): 3D- och 2D-snittpunktmoln, datatabell och etikettmatchad jämförelse tillgängliga; gamutskal, extrahering, tonvärde, uppskattning och validering är inaktiverade.</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Sample</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Prov</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>CxF file is not well-formed XML.</v>
+      </c>
+      <c r="B267" t="str">
+        <v>CxF-filen är inte välformad XML.</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>CxF file contains no colour objects.</v>
+      </c>
+      <c r="B268" t="str">
+        <v>CxF-filen innehåller inga färgobjekt.</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>CxF file contains no CIELab or spectral colour values.</v>
+      </c>
+      <c r="B269" t="str">
+        <v>CxF-filen innehåller inga CIELab- eller spektralfärgvärden.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B264"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B269"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B269"/>
+  <dimension ref="A1:B268"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1275,1293 +1275,1285 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>↻ Regenerate Shell</v>
+        <v>Mesh</v>
       </c>
       <c r="B110" t="str">
-        <v>↻ Återskapa skal</v>
+        <v>Nät</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Mesh</v>
+        <v>Density</v>
       </c>
       <c r="B111" t="str">
-        <v>Nät</v>
+        <v>Densitet</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Density</v>
+        <v>Lighting</v>
       </c>
       <c r="B112" t="str">
-        <v>Densitet</v>
+        <v>Belysning</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Lighting</v>
+        <v>ambient</v>
       </c>
       <c r="B113" t="str">
-        <v>Belysning</v>
+        <v>ambient</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ambient</v>
+        <v>diffuse</v>
       </c>
       <c r="B114" t="str">
-        <v>ambient</v>
+        <v>diffuse</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>diffuse</v>
+        <v>specular</v>
       </c>
       <c r="B115" t="str">
-        <v>diffuse</v>
+        <v>specular</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>specular</v>
+        <v>roughness</v>
       </c>
       <c r="B116" t="str">
-        <v>specular</v>
+        <v>roughness</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>roughness</v>
+        <v>Dataset Settings</v>
       </c>
       <c r="B117" t="str">
-        <v>roughness</v>
+        <v>Datamängdsinställningar</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Dataset Settings</v>
+        <v>Select to toggle file visibility:</v>
       </c>
       <c r="B118" t="str">
-        <v>Datamängdsinställningar</v>
+        <v>Välj för att växla filsynlighet:</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Select to toggle file visibility:</v>
+        <v>Toggle:</v>
       </c>
       <c r="B119" t="str">
-        <v>Välj för att växla filsynlighet:</v>
+        <v>Växla:</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Toggle:</v>
+        <v>Show:</v>
       </c>
       <c r="B120" t="str">
-        <v>Växla:</v>
+        <v>Visa:</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Show:</v>
+        <v>Original</v>
       </c>
       <c r="B121" t="str">
-        <v>Visa:</v>
+        <v>Original</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Original</v>
+        <v>Modified</v>
       </c>
       <c r="B122" t="str">
-        <v>Original</v>
+        <v>Ändrad</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Modified</v>
+        <v>✕ Close</v>
       </c>
       <c r="B123" t="str">
-        <v>Ändrad</v>
+        <v>✕ Stäng</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>✕ Close</v>
+        <v>Selected file is not loaded.</v>
       </c>
       <c r="B124" t="str">
-        <v>✕ Stäng</v>
+        <v>Den valda filen är inte inläst.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Selected file is not loaded.</v>
+        <v>Both files must be loaded.</v>
       </c>
       <c r="B125" t="str">
-        <v>Den valda filen är inte inläst.</v>
+        <v>Båda filerna måste vara inlästa.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Both files must be loaded.</v>
+        <v>No K-only patches matched.</v>
       </c>
       <c r="B126" t="str">
-        <v>Båda filerna måste vara inlästa.</v>
+        <v>Inga enbart K-fläckar matchades.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>No K-only patches matched.</v>
+        <v>No CMY patches matched.</v>
       </c>
       <c r="B127" t="str">
-        <v>Inga enbart K-fläckar matchades.</v>
+        <v>Inga CMY-fläckar matchades.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>No CMY patches matched.</v>
+        <v>Missing CMYK device colorants in Dataset A{name}.</v>
       </c>
       <c r="B128" t="str">
-        <v>Inga CMY-fläckar matchades.</v>
+        <v>CMYK-enhetsfärgämnen saknas i datamängd A{name}.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Missing CMYK device colorants in Dataset A{name}.</v>
+        <v>Missing L*a*b* data in Dataset A{name}.</v>
       </c>
       <c r="B129" t="str">
-        <v>CMYK-enhetsfärgämnen saknas i datamängd A{name}.</v>
+        <v>L*a*b*-data saknas i datamängd A{name}.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Missing L*a*b* data in Dataset A{name}.</v>
+        <v>Paper white patch (0,0,0,0) not found in Dataset A.</v>
       </c>
       <c r="B130" t="str">
-        <v>L*a*b*-data saknas i datamängd A{name}.</v>
+        <v>Pappersvit fläck (0,0,0,0) hittades inte i datamängd A.</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Paper white patch (0,0,0,0) not found in Dataset A.</v>
+        <v>100K solid patch not found in Dataset A.</v>
       </c>
       <c r="B131" t="str">
-        <v>Pappersvit fläck (0,0,0,0) hittades inte i datamängd A.</v>
+        <v>100K heltäckande fläck hittades inte i datamängd A.</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>100K solid patch not found in Dataset A.</v>
+        <v>100CMY solid patch not found in Dataset A.</v>
       </c>
       <c r="B132" t="str">
-        <v>100K heltäckande fläck hittades inte i datamängd A.</v>
+        <v>100CMY heltäckande fläck hittades inte i datamängd A.</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>100CMY solid patch not found in Dataset A.</v>
+        <v>G7 Overall:</v>
       </c>
       <c r="B133" t="str">
-        <v>100CMY heltäckande fläck hittades inte i datamängd A.</v>
+        <v>G7 totalt:</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>G7 Overall:</v>
+        <v>Scale</v>
       </c>
       <c r="B134" t="str">
-        <v>G7 totalt:</v>
+        <v>Skala</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Scale</v>
+        <v>Tolerance</v>
       </c>
       <c r="B135" t="str">
-        <v>Skala</v>
+        <v>Tolerans</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Tolerance</v>
+        <v>K (Black)</v>
       </c>
       <c r="B136" t="str">
-        <v>Tolerans</v>
+        <v>K (Svart)</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>K (Black)</v>
+        <v>K patches ({n})</v>
       </c>
       <c r="B137" t="str">
-        <v>K (Svart)</v>
+        <v>K-fläckar ({n})</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>K patches ({n})</v>
+        <v>CMY patches ({n})</v>
       </c>
       <c r="B138" t="str">
-        <v>K-fläckar ({n})</v>
+        <v>CMY-fläckar ({n})</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>CMY patches ({n})</v>
+        <v>K%</v>
       </c>
       <c r="B139" t="str">
-        <v>CMY-fläckar ({n})</v>
+        <v>K%</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>K%</v>
+        <v>L* meas</v>
       </c>
       <c r="B140" t="str">
-        <v>K%</v>
+        <v>L* mätt</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>L* meas</v>
+        <v>L* aim</v>
       </c>
       <c r="B141" t="str">
-        <v>L* mätt</v>
+        <v>L* mål</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L* aim</v>
+        <v>meas</v>
       </c>
       <c r="B142" t="str">
-        <v>L* mål</v>
+        <v>mätt</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>meas</v>
+        <v>aim</v>
       </c>
       <c r="B143" t="str">
-        <v>mätt</v>
+        <v>mål</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>aim</v>
+        <v>No spectral data — switch to Colour Tone Value (CTV)</v>
       </c>
       <c r="B144" t="str">
-        <v>mål</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>No spectral data — switch to Colour Tone Value (CTV)</v>
-      </c>
-      <c r="B145" t="str">
         <v>Inga spektraldata — växla till färgtonvärde (CTV)</v>
       </c>
     </row>
-    <row r="146" xml:space="preserve">
-      <c r="A146" t="str" xml:space="preserve">
+    <row r="145" xml:space="preserve">
+      <c r="A145" t="str" xml:space="preserve">
         <v xml:space="preserve">No primary tone steps found.
 Needs rows with a single non-zero colorant.</v>
       </c>
-      <c r="B146" t="str" xml:space="preserve">
+      <c r="B145" t="str" xml:space="preserve">
         <v xml:space="preserve">Inga primära tonsteg hittades.
 Kräver rader med ett enda nollskilt färgämne.</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tone Value Gain (%)</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Tonvärdesökning (%)</v>
+      </c>
+    </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Tone Value Gain (%)</v>
+        <v>Tone Value (%)</v>
       </c>
       <c r="B147" t="str">
-        <v>Tonvärdesökning (%)</v>
+        <v>Tonvärde (%)</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Tone Value (%)</v>
+        <v>Input (%)</v>
       </c>
       <c r="B148" t="str">
-        <v>Tonvärde (%)</v>
+        <v>Ingångsvärde (%)</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Input (%)</v>
+        <v>Model fit — degree {deg}, {n} points</v>
       </c>
       <c r="B149" t="str">
-        <v>Ingångsvärde (%)</v>
+        <v>Modellanpassning — grad {deg}, {n} punkter</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Model fit — degree {deg}, {n} points</v>
+        <v>↻ Regenerate</v>
       </c>
       <c r="B150" t="str">
-        <v>Modellanpassning — grad {deg}, {n} punkter</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>↻ Regenerate</v>
-      </c>
-      <c r="B151" t="str">
         <v>↻ Återskapa</v>
+      </c>
+    </row>
+    <row r="151" xml:space="preserve">
+      <c r="A151" t="str" xml:space="preserve">
+        <v xml:space="preserve">Input
+colorant</v>
+      </c>
+      <c r="B151" t="str" xml:space="preserve">
+        <v xml:space="preserve">Ingångs-
+färgämne</v>
       </c>
     </row>
     <row r="152" xml:space="preserve">
       <c r="A152" t="str" xml:space="preserve">
-        <v xml:space="preserve">Input
-colorant</v>
-      </c>
-      <c r="B152" t="str" xml:space="preserve">
-        <v xml:space="preserve">Ingångs-
-färgämne</v>
-      </c>
-    </row>
-    <row r="153" xml:space="preserve">
-      <c r="A153" t="str" xml:space="preserve">
         <v xml:space="preserve">Nearest
 in dataset</v>
       </c>
-      <c r="B153" t="str" xml:space="preserve">
+      <c r="B152" t="str" xml:space="preserve">
         <v xml:space="preserve">Närmaste
 i datamängd</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Model</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Modell</v>
+      </c>
+    </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Model</v>
+        <v>Computing…</v>
       </c>
       <c r="B154" t="str">
-        <v>Modell</v>
+        <v>Beräknar…</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Computing…</v>
+        <v>Calculating tone values…</v>
       </c>
       <c r="B155" t="str">
-        <v>Beräknar…</v>
+        <v>Beräknar tonvärden…</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Calculating tone values…</v>
+        <v>Estimating model…</v>
       </c>
       <c r="B156" t="str">
-        <v>Beräknar tonvärden…</v>
+        <v>Uppskattar modell…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Estimating model…</v>
+        <v>Building 3D gamut…</v>
       </c>
       <c r="B157" t="str">
-        <v>Uppskattar modell…</v>
+        <v>Bygger 3D-gamut…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Building 3D gamut…</v>
+        <v>Computing 2D slice…</v>
       </c>
       <c r="B158" t="str">
-        <v>Bygger 3D-gamut…</v>
+        <v>Beräknar 2D-snitt…</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Computing 2D slice…</v>
+        <v>Rendering…</v>
       </c>
       <c r="B159" t="str">
-        <v>Beräknar 2D-snitt…</v>
+        <v>Renderar…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Rendering…</v>
+        <v>Model fit failed: {msg}</v>
       </c>
       <c r="B160" t="str">
-        <v>Renderar…</v>
+        <v>Modellanpassning misslyckades: {msg}</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Model fit failed: {msg}</v>
+        <v>Retry</v>
       </c>
       <c r="B161" t="str">
-        <v>Modellanpassning misslyckades: {msg}</v>
+        <v>Försök igen</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Retry</v>
+        <v>Click on L*a*b* color to display spectral graph.</v>
       </c>
       <c r="B162" t="str">
-        <v>Försök igen</v>
+        <v>Klicka på L*a*b*-färg för att visa spektraldiagrammet.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Click on L*a*b* color to display spectral graph.</v>
+        <v>Scroll to top</v>
       </c>
       <c r="B163" t="str">
-        <v>Klicka på L*a*b*-färg för att visa spektraldiagrammet.</v>
+        <v>Scrolla till toppen</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Scroll to top</v>
+        <v>Top</v>
       </c>
       <c r="B164" t="str">
-        <v>Scrolla till toppen</v>
+        <v>Toppen</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Top</v>
+        <v>Help</v>
       </c>
       <c r="B165" t="str">
-        <v>Toppen</v>
+        <v>Hjälp</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Help</v>
+        <v>About CharData</v>
       </c>
       <c r="B166" t="str">
-        <v>Hjälp</v>
+        <v>Om CharData</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>About CharData</v>
+        <v>Support on Ko-fi</v>
       </c>
       <c r="B167" t="str">
-        <v>Om CharData</v>
+        <v>Stöd på Ko-fi</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Support on Ko-fi</v>
+        <v>Buy me a coffee</v>
       </c>
       <c r="B168" t="str">
-        <v>Stöd på Ko-fi</v>
+        <v>Bjud mig på en kaffe</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Buy me a coffee</v>
+        <v>Reflectance</v>
       </c>
       <c r="B169" t="str">
-        <v>Bjud mig på en kaffe</v>
+        <v>Reflektans</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Reflectance</v>
+        <v>CharData is free for the color community. If it helps you, a small Ko-fi donation helps keep it running.</v>
       </c>
       <c r="B170" t="str">
-        <v>Reflektans</v>
+        <v>CharData är gratis för färggemenskapen. Om det hjälper dig bidrar en liten Ko-fi-donation till att hålla det igång.</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>CharData is free for the color community. If it helps you, a small Ko-fi donation helps keep it running.</v>
+        <v>Characterization data</v>
       </c>
       <c r="B171" t="str">
-        <v>CharData är gratis för färggemenskapen. Om det hjälper dig bidrar en liten Ko-fi-donation till att hålla det igång.</v>
+        <v>Karakteriseringsdata</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Characterization data</v>
+        <v>ICC Profiles</v>
       </c>
       <c r="B172" t="str">
-        <v>Karakteriseringsdata</v>
+        <v>ICC-profiler</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>ICC Profiles</v>
+        <v>No characterization datasets loaded</v>
       </c>
       <c r="B173" t="str">
-        <v>ICC-profiler</v>
+        <v>Inga karakteriseringsdataset inlästa</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>No characterization datasets loaded</v>
+        <v>No ICC profiles loaded</v>
       </c>
       <c r="B174" t="str">
-        <v>Inga karakteriseringsdataset inlästa</v>
+        <v>Inga ICC-profiler inlästa</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>No ICC profiles loaded</v>
+        <v>Characterization dataset</v>
       </c>
       <c r="B175" t="str">
-        <v>Inga ICC-profiler inlästa</v>
+        <v>Karakteriseringsdataset</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Characterization dataset</v>
+        <v>ICC Profile</v>
       </c>
       <c r="B176" t="str">
-        <v>Karakteriseringsdataset</v>
+        <v>ICC-profil</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>ICC Profile</v>
+        <v>Not a valid ICC profile (header magic missing).</v>
       </c>
       <c r="B177" t="str">
-        <v>ICC-profil</v>
+        <v>Ogiltig ICC-profil (header-signatur saknas).</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Not a valid ICC profile (header magic missing).</v>
+        <v>Standard datasets</v>
       </c>
       <c r="B178" t="str">
-        <v>Ogiltig ICC-profil (header-signatur saknas).</v>
+        <v>Standarddatauppsättningar</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Standard datasets</v>
+        <v>Loading…</v>
       </c>
       <c r="B179" t="str">
-        <v>Standarddatauppsättningar</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading…</v>
+        <v>Failed to load list</v>
       </c>
       <c r="B180" t="str">
-        <v>Läser in…</v>
+        <v>Det gick inte att läsa in listan</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Failed to load list</v>
+        <v>Thickness:</v>
       </c>
       <c r="B181" t="str">
-        <v>Det gick inte att läsa in listan</v>
+        <v>Tjocklek:</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Thickness:</v>
+        <v>Fall-off:</v>
       </c>
       <c r="B182" t="str">
-        <v>Tjocklek:</v>
+        <v>Övergång:</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fall-off:</v>
+        <v>Hard</v>
       </c>
       <c r="B183" t="str">
-        <v>Övergång:</v>
+        <v>Hård</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Hard</v>
+        <v>Soft</v>
       </c>
       <c r="B184" t="str">
-        <v>Hård</v>
+        <v>Mjuk</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Soft</v>
+        <v>G7 validation is not available for ICC profiles.</v>
       </c>
       <c r="B185" t="str">
-        <v>Mjuk</v>
+        <v>G7-validering är inte tillgänglig för ICC-profiler.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>G7 validation is not available for ICC profiles.</v>
+        <v>ICC vs ICC comparison requires identical colorant lists. Profile A: {a}. Profile B: {b}.</v>
       </c>
       <c r="B186" t="str">
-        <v>G7-validering är inte tillgänglig för ICC-profiler.</v>
+        <v>ICC-mot-ICC-jämförelse kräver identiska färgmedelslistor. Profil A: {a}. Profil B: {b}.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>ICC vs ICC comparison requires identical colorant lists. Profile A: {a}. Profile B: {b}.</v>
+        <v>Dataset B does not contain colorants matching ICC profile A.</v>
       </c>
       <c r="B187" t="str">
-        <v>ICC-mot-ICC-jämförelse kräver identiska färgmedelslistor. Profil A: {a}. Profil B: {b}.</v>
+        <v>Datamängd B innehåller inga färgmedel som matchar ICC-profil A.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Dataset B does not contain colorants matching ICC profile A.</v>
+        <v>Dataset A does not contain colorants matching ICC profile B.</v>
       </c>
       <c r="B188" t="str">
-        <v>Datamängd B innehåller inga färgmedel som matchar ICC-profil A.</v>
+        <v>Datamängd A innehåller inga färgmedel som matchar ICC-profil B.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Dataset A does not contain colorants matching ICC profile B.</v>
+        <v>Header</v>
       </c>
       <c r="B189" t="str">
-        <v>Datamängd A innehåller inga färgmedel som matchar ICC-profil B.</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Header</v>
+        <v>Tags</v>
       </c>
       <c r="B190" t="str">
-        <v>Header</v>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Tags</v>
+        <v>Loading ICC viewer…</v>
       </c>
       <c r="B191" t="str">
-        <v>Taggar</v>
+        <v>Läser in ICC-visare…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Loading ICC viewer…</v>
+        <v>Launch editor</v>
       </c>
       <c r="B192" t="str">
-        <v>Läser in ICC-visare…</v>
+        <v>Öppna redigerare</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Launch editor</v>
+        <v>All data stays local to browser</v>
       </c>
       <c r="B193" t="str">
-        <v>Öppna redigerare</v>
+        <v>All data stannar lokalt i webbläsaren</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>All data stays local to browser</v>
+        <v>Free browser-resident online tool</v>
       </c>
       <c r="B194" t="str">
-        <v>All data stannar lokalt i webbläsaren</v>
+        <v>Gratis onlineverktyg som körs i webbläsaren</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Free browser-resident online tool</v>
+        <v>Image</v>
       </c>
       <c r="B195" t="str">
-        <v>Gratis onlineverktyg som körs i webbläsaren</v>
+        <v>Bild</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Image</v>
+        <v>Load Image</v>
       </c>
       <c r="B196" t="str">
-        <v>Bild</v>
+        <v>Läs in bild</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Load Image</v>
+        <v>Bind image to dataset</v>
       </c>
       <c r="B197" t="str">
-        <v>Läs in bild</v>
+        <v>Koppla bild till dataset</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Bind image to dataset</v>
+        <v>Remove image</v>
       </c>
       <c r="B198" t="str">
-        <v>Koppla bild till dataset</v>
+        <v>Ta bort bild</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Remove image</v>
+        <v>Image color space: {cs} {src}</v>
       </c>
       <c r="B199" t="str">
-        <v>Ta bort bild</v>
+        <v>Bildens färgrymd: {cs} {src}</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Image color space: {cs} {src}</v>
+        <v>Bound to {name} — {n} points</v>
       </c>
       <c r="B200" t="str">
-        <v>Bildens färgrymd: {cs} {src}</v>
+        <v>Kopplad till {name} — {n} punkter</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Bound to {name} — {n} points</v>
+        <v>Lab image — {n} points</v>
       </c>
       <c r="B201" t="str">
-        <v>Kopplad till {name} — {n} punkter</v>
+        <v>Lab-bild — {n} punkter</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Lab image — {n} points</v>
+        <v>Cannot bind: image is {img} but Dataset {slot} is {family}.</v>
       </c>
       <c r="B202" t="str">
-        <v>Lab-bild — {n} punkter</v>
+        <v>Kan inte koppla: bilden är {img} men dataset {slot} är {family}.</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Cannot bind: image is {img} but Dataset {slot} is {family}.</v>
+        <v>Unsupported image format. Use PNG, JPEG, TIFF, BMP, GIF, or PDF.</v>
       </c>
       <c r="B203" t="str">
-        <v>Kan inte koppla: bilden är {img} men dataset {slot} är {family}.</v>
+        <v>Bildformatet stöds inte. Använd PNG, JPEG, TIFF, BMP, GIF eller PDF.</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Unsupported image format. Use PNG, JPEG, TIFF, BMP, GIF, or PDF.</v>
+        <v>“{name}” is too large ({mb} MB). Maximum image size is {max} MB.</v>
       </c>
       <c r="B204" t="str">
-        <v>Bildformatet stöds inte. Använd PNG, JPEG, TIFF, BMP, GIF eller PDF.</v>
+        <v>”{name}” är för stor ({mb} MB). Maximal bildstorlek: {max} MB.</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>“{name}” is too large ({mb} MB). Maximum image size is {max} MB.</v>
+        <v>Embedded: {name}</v>
       </c>
       <c r="B205" t="str">
-        <v>”{name}” är för stor ({mb} MB). Maximal bildstorlek: {max} MB.</v>
+        <v>Inbäddad: {name}</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Embedded: {name}</v>
+        <v>Decoding image…</v>
       </c>
       <c r="B206" t="str">
-        <v>Inbäddad: {name}</v>
+        <v>Avkodar bild…</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Decoding image…</v>
+        <v>Image file is too small or corrupt.</v>
       </c>
       <c r="B207" t="str">
-        <v>Avkodar bild…</v>
+        <v>Bildfilen är för liten eller skadad.</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Image file is too small or corrupt.</v>
+        <v>TIFF decoder library failed to load.</v>
       </c>
       <c r="B208" t="str">
-        <v>Bildfilen är för liten eller skadad.</v>
+        <v>TIFF-avkodningsbiblioteket kunde inte läsas in.</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>TIFF decoder library failed to load.</v>
+        <v>Selected dataset model is still loading — try again in a moment.</v>
       </c>
       <c r="B209" t="str">
-        <v>TIFF-avkodningsbiblioteket kunde inte läsas in.</v>
+        <v>Det valda dataset-modellen läses fortfarande in — försök igen om en stund.</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Selected dataset model is still loading — try again in a moment.</v>
+        <v>Image decode failed.</v>
       </c>
       <c r="B210" t="str">
-        <v>Det valda dataset-modellen läses fortfarande in — försök igen om en stund.</v>
+        <v>Bildavkodningen misslyckades.</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Image decode failed.</v>
+        <v>No color dataset loaded.</v>
       </c>
       <c r="B211" t="str">
-        <v>Bildavkodningen misslyckades.</v>
+        <v>Inget färgdataset har lästs in.</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>No color dataset loaded.</v>
+        <v>Embedded profile is no longer available.</v>
       </c>
       <c r="B212" t="str">
-        <v>Inget färgdataset har lästs in.</v>
+        <v>Den inbäddade profilen är inte längre tillgänglig.</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Embedded profile is no longer available.</v>
+        <v>(from embedded ICC)</v>
       </c>
       <c r="B213" t="str">
-        <v>Den inbäddade profilen är inte längre tillgänglig.</v>
+        <v>(från inbäddad ICC)</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>(from embedded ICC)</v>
+        <v>(TIFF Lab)</v>
       </c>
       <c r="B214" t="str">
-        <v>(från inbäddad ICC)</v>
+        <v>(TIFF Lab)</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>(TIFF Lab)</v>
+        <v>(inferred from channels)</v>
       </c>
       <c r="B215" t="str">
-        <v>(TIFF Lab)</v>
+        <v>(härlett från kanaler)</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>(inferred from channels)</v>
+        <v>{n} representative points after binning + dedupe</v>
       </c>
       <c r="B216" t="str">
-        <v>(härlett från kanaler)</v>
+        <v>{n} representativa punkter efter binning + deduplicering</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>{n} representative points after binning + dedupe</v>
+        <v>PDF support is limited to single-image Photoshop PDFs. Save as TIFF, JPEG, PNG, BMP, or GIF for other PDF content.</v>
       </c>
       <c r="B217" t="str">
-        <v>{n} representativa punkter efter binning + deduplicering</v>
+        <v>PDF-stöd är begränsat till Photoshop-PDF med en enda bild. Spara som TIFF, JPEG, PNG, BMP eller GIF för annat PDF-innehåll.</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PDF support is limited to single-image Photoshop PDFs. Save as TIFF, JPEG, PNG, BMP, or GIF for other PDF content.</v>
+        <v>Encrypted PDFs are not supported.</v>
       </c>
       <c r="B218" t="str">
-        <v>PDF-stöd är begränsat till Photoshop-PDF med en enda bild. Spara som TIFF, JPEG, PNG, BMP eller GIF för annat PDF-innehåll.</v>
+        <v>Krypterade PDF:er stöds inte.</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Encrypted PDFs are not supported.</v>
+        <v>Only single-page Photoshop PDFs are supported.</v>
       </c>
       <c r="B219" t="str">
-        <v>Krypterade PDF:er stöds inte.</v>
+        <v>Endast ensidiga Photoshop-PDF:er stöds.</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Only single-page Photoshop PDFs are supported.</v>
+        <v>PDF structure could not be parsed.</v>
       </c>
       <c r="B220" t="str">
-        <v>Endast ensidiga Photoshop-PDF:er stöds.</v>
+        <v>PDF-strukturen kunde inte tolkas.</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>PDF structure could not be parsed.</v>
+        <v>No image found inside the PDF.</v>
       </c>
       <c r="B221" t="str">
-        <v>PDF-strukturen kunde inte tolkas.</v>
+        <v>Ingen bild hittades i PDF:en.</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>No image found inside the PDF.</v>
+        <v>PDF colour space is not supported. Use Gray, RGB, CMYK, or an ICC-based profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>Ingen bild hittades i PDF:en.</v>
+        <v>PDF-färgrymden stöds inte. Använd Grå, RGB, CMYK eller en ICC-baserad profil.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>PDF colour space is not supported. Use Gray, RGB, CMYK, or an ICC-based profile.</v>
+        <v>PDF image filter is not supported. Re-save the PDF with JPEG or ZIP compression.</v>
       </c>
       <c r="B223" t="str">
-        <v>PDF-färgrymden stöds inte. Använd Grå, RGB, CMYK eller en ICC-baserad profil.</v>
+        <v>PDF-bildfiltret stöds inte. Spara om PDF:en med JPEG- eller ZIP-komprimering.</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>PDF image filter is not supported. Re-save the PDF with JPEG or ZIP compression.</v>
+        <v>Close file select</v>
       </c>
       <c r="B224" t="str">
-        <v>PDF-bildfiltret stöds inte. Spara om PDF:en med JPEG- eller ZIP-komprimering.</v>
+        <v>Stäng filval</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close file select</v>
+        <v>Drag to resize</v>
       </c>
       <c r="B225" t="str">
-        <v>Stäng filval</v>
+        <v>Dra för att ändra storlek</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Drag to resize</v>
+        <v>Contact</v>
       </c>
       <c r="B226" t="str">
-        <v>Dra för att ändra storlek</v>
+        <v>Kontakt</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Contact</v>
+        <v>Remove file</v>
       </c>
       <c r="B227" t="str">
-        <v>Kontakt</v>
+        <v>Ta bort fil</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Remove file</v>
+        <v>Rendering intent:</v>
       </c>
       <c r="B228" t="str">
-        <v>Ta bort fil</v>
+        <v>Renderingsintention:</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Rendering intent:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B229" t="str">
-        <v>Renderingsintention:</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Perceptual</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B230" t="str">
-        <v>Perceptuell</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B231" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Saturation</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B232" t="str">
-        <v>Mättnad</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>System default ({lang})</v>
       </c>
       <c r="B233" t="str">
-        <v>Absolut kolorimetrisk</v>
+        <v>Systemstandard ({lang})</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>System default ({lang})</v>
+        <v>ICC load error: {msg}</v>
       </c>
       <c r="B234" t="str">
-        <v>Systemstandard ({lang})</v>
+        <v>ICC-laddningsfel: {msg}</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC load error: {msg}</v>
+        <v>Could not parse ICC profile: {msg}</v>
       </c>
       <c r="B235" t="str">
-        <v>ICC-laddningsfel: {msg}</v>
+        <v>Det gick inte att tolka ICC-profilen: {msg}</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Could not parse ICC profile: {msg}</v>
+        <v>Popup blocked — allow popups for this site to launch the editor.</v>
       </c>
       <c r="B236" t="str">
-        <v>Det gick inte att tolka ICC-profilen: {msg}</v>
+        <v>Popup blockerad — tillåt popup-fönster för den här webbplatsen för att starta redigeraren.</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Popup blocked — allow popups for this site to launch the editor.</v>
+        <v>Failed to load {name}: {msg}</v>
       </c>
       <c r="B237" t="str">
-        <v>Popup blockerad — tillåt popup-fönster för den här webbplatsen för att starta redigeraren.</v>
+        <v>Det gick inte att läsa in {name}: {msg}</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Failed to load {name}: {msg}</v>
+        <v>Color space</v>
       </c>
       <c r="B238" t="str">
-        <v>Det gick inte att läsa in {name}: {msg}</v>
+        <v>Färgrymd</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Color space</v>
+        <v>Device class</v>
       </c>
       <c r="B239" t="str">
-        <v>Färgrymd</v>
+        <v>Enhetsklass</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Device class</v>
+        <v>Colorants</v>
       </c>
       <c r="B240" t="str">
-        <v>Enhetsklass</v>
+        <v>Färgmedel</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Colorants</v>
+        <v>Rendering intents</v>
       </c>
       <c r="B241" t="str">
-        <v>Färgmedel</v>
+        <v>Renderingsintentioner</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Rendering intents</v>
+        <v>ICC A2B Evaluation</v>
       </c>
       <c r="B242" t="str">
-        <v>Renderingsintentioner</v>
+        <v>ICC A2B-utvärdering</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>ICC A2B Evaluation</v>
+        <v>ICC Output</v>
       </c>
       <c r="B243" t="str">
-        <v>ICC A2B-utvärdering</v>
+        <v>ICC-utdata</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>ICC Output</v>
+        <v>Image detail</v>
       </c>
       <c r="B244" t="str">
-        <v>ICC-utdata</v>
+        <v>Bilddetalj</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Image detail</v>
+        <v>Coarse</v>
       </c>
       <c r="B245" t="str">
-        <v>Bilddetalj</v>
+        <v>Grov</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Coarse</v>
+        <v>Standard</v>
       </c>
       <c r="B246" t="str">
-        <v>Grov</v>
+        <v>Standard</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Standard</v>
+        <v>Fine</v>
       </c>
       <c r="B247" t="str">
-        <v>Standard</v>
+        <v>Fin</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Fine</v>
+        <v>Subscribe</v>
       </c>
       <c r="B248" t="str">
-        <v>Fin</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new chardata releases</v>
       </c>
       <c r="B249" t="str">
-        <v>Prenumerera</v>
+        <v>Få besked om nya chardata-releaser</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Get notified about new chardata releases</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B250" t="str">
-        <v>Få besked om nya chardata-releaser</v>
+        <v>Få besked om nya releaser</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Get notified about new releases</v>
+        <v>Close</v>
       </c>
       <c r="B251" t="str">
-        <v>Få besked om nya releaser</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor chardata release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B252" t="str">
-        <v>Stäng</v>
+        <v>Vi mejlar dig när en ny större eller mindre chardata-release släpps. Patch-releaser hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>We’ll email you when a new major or minor chardata release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Email address</v>
       </c>
       <c r="B253" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre chardata-release släpps. Patch-releaser hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Email address</v>
+        <v>you@example.com</v>
       </c>
       <c r="B254" t="str">
-        <v>E-postadress</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>you@example.com</v>
+        <v>How will you use chardata?</v>
       </c>
       <c r="B255" t="str">
-        <v>du@exempel.com</v>
+        <v>Hur kommer du att använda chardata?</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>How will you use chardata?</v>
+        <v>(optional)</v>
       </c>
       <c r="B256" t="str">
-        <v>Hur kommer du att använda chardata?</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>(optional)</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B257" t="str">
-        <v>(valfritt)</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>I agree to receive emails about chardata releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B258" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Jag godkänner att få e-post om chardata-releaser. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>I agree to receive emails about chardata releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B259" t="str">
-        <v>Jag godkänner att få e-post om chardata-releaser. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Subscribe</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B260" t="str">
-        <v>Prenumerera</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new chardata release ships.</v>
       </c>
       <c r="B261" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>När du har godkänts får du ett välkomstmeddelande. Sedan hör vi av oss endast när en ny chardata-release släpps.</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new chardata release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B262" t="str">
-        <v>När du har godkänts får du ett välkomstmeddelande. Sedan hör vi av oss endast när en ny chardata-release släpps.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Close</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B263" t="str">
-        <v>Stäng</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Privacy notice</v>
+        <v>Measurement-only data (no device colorants): 3D and 2D-slice point cloud, data table, and label-matched compare are available; gamut shell, extract, tone value, estimate, and validation are disabled.</v>
       </c>
       <c r="B264" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Endast mätdata (inga enhetsfärgämnen): 3D- och 2D-snittpunktmoln, datatabell och etikettmatchad jämförelse tillgängliga; gamutskal, extrahering, tonvärde, uppskattning och validering är inaktiverade.</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Measurement-only data (no device colorants): 3D and 2D-slice point cloud, data table, and label-matched compare are available; gamut shell, extract, tone value, estimate, and validation are disabled.</v>
+        <v>Sample</v>
       </c>
       <c r="B265" t="str">
-        <v>Endast mätdata (inga enhetsfärgämnen): 3D- och 2D-snittpunktmoln, datatabell och etikettmatchad jämförelse tillgängliga; gamutskal, extrahering, tonvärde, uppskattning och validering är inaktiverade.</v>
+        <v>Prov</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Sample</v>
+        <v>CxF file is not well-formed XML.</v>
       </c>
       <c r="B266" t="str">
-        <v>Prov</v>
+        <v>CxF-filen är inte välformad XML.</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>CxF file is not well-formed XML.</v>
+        <v>CxF file contains no colour objects.</v>
       </c>
       <c r="B267" t="str">
-        <v>CxF-filen är inte välformad XML.</v>
+        <v>CxF-filen innehåller inga färgobjekt.</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>CxF file contains no colour objects.</v>
+        <v>CxF file contains no CIELab or spectral colour values.</v>
       </c>
       <c r="B268" t="str">
-        <v>CxF-filen innehåller inga färgobjekt.</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="str">
-        <v>CxF file contains no CIELab or spectral colour values.</v>
-      </c>
-      <c r="B269" t="str">
         <v>CxF-filen innehåller inga CIELab- eller spektralfärgvärden.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B269"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B268"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B270"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2551,9 +2551,25 @@
         <v>CxF-filen innehåller inga CIELab- eller spektralfärgvärden.</v>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>IT8.7/5 Patches ({n})</v>
+      </c>
+      <c r="B269" t="str">
+        <v>IT8.7/5-färgrutor ({n})</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>Device Patches ({n})</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Enhetsfärgrutor ({n})</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B268"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B270"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B270"/>
+  <dimension ref="A1:B273"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2567,9 +2567,33 @@
         <v>Enhetsfärgrutor ({n})</v>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Number format</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Talformat</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>Hexadecimal</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Hexadecimal</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Decimal</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Decimal</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B270"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B273"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B273"/>
+  <dimension ref="A1:B308"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2591,9 +2591,289 @@
         <v>Decimal</v>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Taggnamn</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B275" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Storlek</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Utfyllnad</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Inga taggar hittades.</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Array of</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Array av</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Profil-ID</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Läser in fullständig beskrivning…</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v xml:space="preserve">Could not load full description: </v>
+      </c>
+      <c r="B284" t="str">
+        <v xml:space="preserve">Det gick inte att läsa in den fullständiga beskrivningen: </v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B285" t="str">
+        <v>(Inget innehåll)</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Neutral = in gamut</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Neutral = inom gamut</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Red = out of gamut</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Röd = utanför gamut</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>No CLUT grid</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Inget CLUT-rutnät</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Float</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Flyttal</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Grid</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Rutnät</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>PCS → Device</v>
+      </c>
+      <c r="B291" t="str">
+        <v>PCS → Enhet</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>Device → PCS</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Enhet → PCS</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Input</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Indata</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Output</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Utdata</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Human</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Läsbar</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Norm</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Norm.</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Chromaticity</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Kromaticitet</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Tone curve</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Tonkurva</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>Curve table</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Kurvtabell</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Scatter</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Spridningsdiagram</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Tables</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Tabeller</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Curves</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Kurvor</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Input curves</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Indatakurvor</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Output curves</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Utdatakurvor</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>CLUT</v>
+      </c>
+      <c r="B305" t="str">
+        <v>CLUT</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Gamut</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Gamut</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>Evaluate</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Utvärdera</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Data</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Data</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B273"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B308"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B308"/>
+  <dimension ref="A1:B309"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2871,9 +2871,17 @@
         <v>Data</v>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Spot ink characterisation (CxF/X-4): tint levels are loaded as device colorant values; gamut shell, estimate, and model generation are disabled.</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Dekorfärgskarakterisering (CxF/X-4): tonvärdesnivåer läses in som enhetsfärgämnesvärden; gamutskal, uppskattning och modellgenerering är inaktiverade.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B308"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B309"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B309"/>
+  <dimension ref="A1:B310"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2879,9 +2879,17 @@
         <v>Dekorfärgskarakterisering (CxF/X-4): tonvärdesnivåer läses in som enhetsfärgämnesvärden; gamutskal, uppskattning och modellgenerering är inaktiverade.</v>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Reset zoom</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Återställ zoom</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B309"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B310"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B310"/>
+  <dimension ref="A1:B315"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2887,9 +2887,49 @@
         <v>Återställ zoom</v>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>Colorimetry Source</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Kolorimetrikälla</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>Prefer spectral</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Föredra spektral</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>Use file LAB</v>
+      </c>
+      <c r="B313" t="str">
+        <v>Använd filens LAB</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>File has both spectral and LAB; using LAB computed from spectral per preference.</v>
+      </c>
+      <c r="B314" t="str">
+        <v>Filen har både spektral och LAB; LAB beräknat från spektral enligt inställning.</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>File has both spectral and LAB; using the file’s LAB per preference.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Filen har både spektral och LAB; använder filens LAB enligt inställning.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B310"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B315"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B315"/>
+  <dimension ref="A1:B319"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2927,9 +2927,41 @@
         <v>Filen har både spektral och LAB; använder filens LAB enligt inställning.</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Zoom in</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Zooma in</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>Zoom out</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Zooma ut</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>Reset to fit</v>
+      </c>
+      <c r="B318" t="str">
+        <v>Återställ till anpassning</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>Drag to resize</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Dra för att ändra storlek</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B315"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B320"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2959,9 +2959,17 @@
         <v>Dra för att ändra storlek</v>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Show gamut wireframe</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Visa gamutnät</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B320"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B327"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2967,9 +2967,65 @@
         <v>Visa gamutnät</v>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Comparison Statistics</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Jämförelsestatistik</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Relative frequency</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Relativ frekvens</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Cumulative frequency</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Kumulativ frekvens</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Horizontal scale</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Horisontell skala</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>Integer ΔE</v>
+      </c>
+      <c r="B325" t="str">
+        <v>Heltals-ΔE</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>Auto-scale</v>
+      </c>
+      <c r="B326" t="str">
+        <v>Autoskala</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>Bins</v>
+      </c>
+      <c r="B327" t="str">
+        <v>Fack</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B320"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B327"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B327"/>
+  <dimension ref="A1:B334"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3023,9 +3023,65 @@
         <v>Fack</v>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Rotation</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Rotation</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>Mode:</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Läge:</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>Turntable</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Vridskiva</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Orbit</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Orbit</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Drag rotate sensitivity:</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Känslighet för dragrotation:</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Enable roll (horizontal scroll)</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Aktivera rullning (horisontell scroll)</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Roll sensitivity:</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Rullningskänslighet:</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B327"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B334"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B334"/>
+  <dimension ref="A1:B377"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3079,9 +3079,353 @@
         <v>Rullningskänslighet:</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Primaries &amp; Overprints</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Primärer och övertryck</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>Patch</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Färgruta</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Paper</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Papper</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>Cyan</v>
+      </c>
+      <c r="B338" t="str">
+        <v>Cyan</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>Magenta</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Magenta</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>Yellow</v>
+      </c>
+      <c r="B340" t="str">
+        <v>Gul</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>Black</v>
+      </c>
+      <c r="B341" t="str">
+        <v>Svart</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>Red</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Röd</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Green</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Grön</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Blue</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Blå</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>CMY</v>
+      </c>
+      <c r="B345" t="str">
+        <v>CMY</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>CMYK</v>
+      </c>
+      <c r="B346" t="str">
+        <v>CMYK</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Found {n} duplicate measurements in the original dataset.</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Hittade {n} dubbletter av mätningar i den ursprungliga datamängden.</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Found {n} duplicate measurements in the original dataset (repeatability ΔE mean {mean}, max {max}).</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Hittade {n} dubbletter av mätningar i den ursprungliga datamängden (repeterbarhet ΔE medel {mean}, max {max}).</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Near-Neutral Survey</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Analys av nära-neutrala</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Threshold (ΔE*ab)</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Tröskel (ΔE*ab)</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>{near} of {total} patches within {thr} ΔE of neutral.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>{near} av {total} rutor inom {thr} ΔE från neutralt.</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>No patches within {thr} ΔE of neutral.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Inga rutor inom {thr} ΔE från neutralt.</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Distance from neutral (ΔE*ab)</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Avstånd från neutralt (ΔE*ab)</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Near-neutral</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Nära-neutral</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Other patches</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Övriga rutor</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Comparison Plot</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Jämförelsediagram</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>P90 = {v}</v>
+      </c>
+      <c r="B357" t="str">
+        <v>P90 = {v}</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Percentiles</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Percentiler</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Per-channel ΔE</v>
+      </c>
+      <c r="B359" t="str">
+        <v>ΔE per kanal</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Included: patches using this ink (&gt;0). Excluded: patches without it. Only: this ink alone.</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Inkluderade: rutor som använder denna färg (&gt;0). Exkluderade: rutor utan den. Endast: enbart denna färg.</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Included</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Inkluderade</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Excluded</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Exkluderade</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Only</v>
+      </c>
+      <c r="B363" t="str">
+        <v>Endast</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>N</v>
+      </c>
+      <c r="B364" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>P90</v>
+      </c>
+      <c r="B365" t="str">
+        <v>P90</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>P95</v>
+      </c>
+      <c r="B366" t="str">
+        <v>P95</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Max</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Max</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Användarhandbok</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Search the guide…</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Sök i handboken…</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Previous match</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Föregående träff</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Next match</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Nästa träff</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Open in a new tab</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Öppna i ny flik</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>Loading the guide…</v>
+      </c>
+      <c r="B373" t="str">
+        <v>Läser in handboken…</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>Couldn’t load the guide. Try opening it in a new tab.</v>
+      </c>
+      <c r="B374" t="str">
+        <v>Det gick inte att läsa in handboken. Prova att öppna den i en ny flik.</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>No matches</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Inga träffar</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>{i}/{n}</v>
+      </c>
+      <c r="B376" t="str">
+        <v>{i}/{n}</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>Image is too large to process safely.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Bilden är för stor för att bearbetas säkert.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B334"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B377"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B386"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3423,9 +3423,81 @@
         <v>Bilden är för stor för att bearbetas säkert.</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>L* Reversal</v>
+      </c>
+      <c r="B378" t="str">
+        <v>L*-omvändning</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>Adding ink to a single-ink tint ramp should only darken it. Each measured ramp is checked; any step where L* rises is flagged as a reversal.</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Att lägga till färg på en enfärgs-tonramp ska bara göra den mörkare. Varje uppmätt ramp kontrolleras; varje steg där L* stiger flaggas som en omvändning.</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Threshold (ΔL*)</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Tröskel (ΔL*)</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>{n} reversal(s) across {cols} ink ramp(s).</v>
+      </c>
+      <c r="B381" t="str">
+        <v>{n} omvändning(ar) över {cols} färgramp(er).</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>No L* reversals — every ink ramp darkens monotonically.</v>
+      </c>
+      <c r="B382" t="str">
+        <v>Inga L*-omvändningar — varje färgramp mörknar monotont.</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>L* reversal</v>
+      </c>
+      <c r="B383" t="str">
+        <v>L*-omvändning</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Ink %</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Färg %</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Colorant</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Färgämne</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>Ink range</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Färgintervall</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B377"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B386"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B386"/>
+  <dimension ref="A1:B398"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3433,10 +3433,10 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Adding ink to a single-ink tint ramp should only darken it. Each measured ramp is checked; any step where L* rises is flagged as a reversal.</v>
+        <v>Adding ink to any one channel should only darken the print — whatever the other inks are set to. Each ink channel is checked against every background of the other inks; any pair where more ink gives a higher L* (a lighter result) is a reversal, flagging a measurement error, ink-limit / trapping artefact, or mislabelled patch.</v>
       </c>
       <c r="B379" t="str">
-        <v>Att lägga till färg på en enfärgs-tonramp ska bara göra den mörkare. Varje uppmätt ramp kontrolleras; varje steg där L* stiger flaggas som en omvändning.</v>
+        <v>Att lägga till färg i en enda kanal ska bara göra utskriften mörkare — oavsett hur de andra färgerna är inställda. Varje färgkanal kontrolleras mot varje bakgrund av de andra färgerna; varje par där mer färg ger ett högre L* (ett ljusare resultat) är en omvändning, vilket signalerar ett mätfel, en färgmängds-/trapping-artefakt eller en felmärkt ruta.</v>
       </c>
     </row>
     <row r="380">
@@ -3449,18 +3449,18 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>{n} reversal(s) across {cols} ink ramp(s).</v>
+        <v>{n} reversal(s) above the threshold across {cols} ink channel(s).</v>
       </c>
       <c r="B381" t="str">
-        <v>{n} omvändning(ar) över {cols} färgramp(er).</v>
+        <v>{n} omvändning(ar) över tröskeln i {cols} färgkanal(er).</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>No L* reversals — every ink ramp darkens monotonically.</v>
+        <v>No L* reversals above the threshold — every ink darkens monotonically across all backgrounds.</v>
       </c>
       <c r="B382" t="str">
-        <v>Inga L*-omvändningar — varje färgramp mörknar monotont.</v>
+        <v>Inga L*-omvändningar över tröskeln — varje färg mörknar monotont över alla bakgrunder.</v>
       </c>
     </row>
     <row r="383">
@@ -3495,9 +3495,105 @@
         <v>Färgintervall</v>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Channel</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Kanal</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Ink (low → high)</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Färg (låg → hög)</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>All</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Alla</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Show more ({n})</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Visa fler ({n})</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Per-channel summary</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Sammanfattning per kanal</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Samples</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Prover</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>Mean ΔL*</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Medel ΔL*</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>SD</v>
+      </c>
+      <c r="B394" t="str">
+        <v>SD</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Max ΔL*</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Max ΔL*</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v># &gt; ε</v>
+      </c>
+      <c r="B396" t="str">
+        <v># &gt; ε</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>{pts} patches · {ramps} ramps examined · {rev} reversals</v>
+      </c>
+      <c r="B397" t="str">
+        <v>{pts} rutor · {ramps} ramper undersökta · {rev} omvändningar</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Channels with many reversals list only the largest {n} by ΔL*.</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Kanaler med många omvändningar visar bara de {n} största efter ΔL*.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B386"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B398"/>
   </ignoredErrors>
 </worksheet>
 </file>